--- a/artfynd/A 26563-2026 artfynd.xlsx
+++ b/artfynd/A 26563-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124644027</v>
+        <v>124644251</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,11 +713,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572406</v>
+        <v>572344</v>
       </c>
       <c r="R2" t="n">
-        <v>6617298</v>
+        <v>6617288</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +772,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,55 +790,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124644167</v>
+        <v>124644404</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572362</v>
+        <v>572320</v>
       </c>
       <c r="R3" t="n">
-        <v>6617266</v>
+        <v>6617300</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,7 +878,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gammal ogallrad blandskog</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,42 +901,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124644565</v>
+        <v>124644027</v>
       </c>
       <c r="B4" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -967,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572310</v>
+        <v>572406</v>
       </c>
       <c r="R4" t="n">
-        <v>6617249</v>
+        <v>6617298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1002,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal grov gran, tallskog</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,42 +1020,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124644143</v>
+        <v>124644167</v>
       </c>
       <c r="B5" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1144,6 +1136,332 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124644143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Apalbomossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572362</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6617266</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal ogallrad blandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124644565</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Apalbomossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572310</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6617249</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gammal grov gran, tallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124644636</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Apalbomossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572354</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6617194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>i traktorspår.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26563-2026 artfynd.xlsx
+++ b/artfynd/A 26563-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644251</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644404</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644027</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644167</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,6 +1268,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644143</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644565</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,8 +1497,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124644636</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>